--- a/download/sd.xlsx
+++ b/download/sd.xlsx
@@ -71,7 +71,7 @@
     <t>Updated Value 7</t>
   </si>
   <si>
-    <t>21:11</t>
+    <t>6:12</t>
   </si>
 </sst>
 </file>
